--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129676978</v>
+        <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>89033</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4395</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lädervaxing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cuphophyllus russocoriaceus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Jos.K.Miller) Bon</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+          <t>Gisselåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608755</v>
+        <v>608787</v>
       </c>
       <c r="R2" t="n">
-        <v>6919114</v>
+        <v>6919148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,16 +776,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129676978</t>
+          <t>https://artportalen.se/Sighting/137214429</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129677063</v>
+        <v>129676978</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>89033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4395</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lädervaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cuphophyllus russocoriaceus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; Jos.K.Miller) Bon</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608747</v>
+        <v>608755</v>
       </c>
       <c r="R3" t="n">
-        <v>6919181</v>
+        <v>6919114</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,13 +878,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129677063</t>
+          <t>https://artportalen.se/Sighting/129676978</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129680287</v>
+        <v>129677063</v>
       </c>
       <c r="B4" t="n">
         <v>57953</v>
@@ -913,28 +913,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gisselåsen, Söderåsen, Selånger, Mpd</t>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608812</v>
+        <v>608747</v>
       </c>
       <c r="R4" t="n">
-        <v>6919133</v>
+        <v>6919181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,51 +980,63 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129680287</t>
+          <t>https://artportalen.se/Sighting/129677063</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129677052</v>
+        <v>129680287</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+          <t>Gisselåsen, Söderåsen, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608761</v>
+        <v>608812</v>
       </c>
       <c r="R5" t="n">
-        <v>6919168</v>
+        <v>6919133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,51 +1094,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129677052</t>
+          <t>https://artportalen.se/Sighting/129680287</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129677092</v>
+        <v>137214159</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+          <t>Gisselåsen, Söderåsen, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608742</v>
+        <v>608774</v>
       </c>
       <c r="R6" t="n">
-        <v>6919174</v>
+        <v>6919178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,16 +1196,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129677092</t>
+          <t>https://artportalen.se/Sighting/137214159</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129677106</v>
+        <v>137212819</v>
       </c>
       <c r="B7" t="n">
-        <v>106243</v>
+        <v>58667</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,34 +1213,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103046</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Acanthis flammea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+          <t>Gisselåsen, Söderåsen, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608716</v>
+        <v>608723</v>
       </c>
       <c r="R7" t="n">
-        <v>6919160</v>
+        <v>6919186</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,51 +1298,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129677106</t>
+          <t>https://artportalen.se/Sighting/137212819</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129675462</v>
+        <v>129677052</v>
       </c>
       <c r="B8" t="n">
-        <v>57132</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmanstorpet, Västeråsen  Selånger, Mpd</t>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609145</v>
+        <v>608761</v>
       </c>
       <c r="R8" t="n">
-        <v>6919165</v>
+        <v>6919168</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,13 +1400,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129675462</t>
+          <t>https://artportalen.se/Sighting/129677052</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129675371</v>
+        <v>129677092</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1437,14 +1437,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmanstorpet, Bergmanstorpet, Mpd</t>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609172</v>
+        <v>608742</v>
       </c>
       <c r="R9" t="n">
-        <v>6919144</v>
+        <v>6919174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,51 +1502,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129675371</t>
+          <t>https://artportalen.se/Sighting/129677092</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129675720</v>
+        <v>129677106</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>106243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmanstorpet, Bergmanstorpet, Mpd</t>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609174</v>
+        <v>608716</v>
       </c>
       <c r="R10" t="n">
-        <v>6919130</v>
+        <v>6919160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,51 +1604,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129675720</t>
+          <t>https://artportalen.se/Sighting/129677106</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129676730</v>
+        <v>129675462</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+          <t>Bergmanstorpet, Västeråsen  Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608827</v>
+        <v>609145</v>
       </c>
       <c r="R11" t="n">
-        <v>6919124</v>
+        <v>6919165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,6 +1705,312 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675462</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129675371</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergmanstorpet, Bergmanstorpet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>609172</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6919144</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675371</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129675720</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergmanstorpet, Bergmanstorpet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>609174</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6919130</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675720</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129676730</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>608827</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6919124</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129676730</t>
         </is>
@@ -1722,6 +2028,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>137214159</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137212819</v>
       </c>
       <c r="B7" t="n">
-        <v>58667</v>
+        <v>58680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>137214159</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137212819</v>
       </c>
       <c r="B7" t="n">
-        <v>58680</v>
+        <v>58682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>137214159</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137212819</v>
       </c>
       <c r="B7" t="n">
-        <v>58682</v>
+        <v>58692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,45 +1610,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129675462</v>
+        <v>129676714</v>
       </c>
       <c r="B11" t="n">
-        <v>57132</v>
+        <v>92591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmanstorpet, Västeråsen  Selånger, Mpd</t>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609145</v>
+        <v>608827</v>
       </c>
       <c r="R11" t="n">
-        <v>6919165</v>
+        <v>6919124</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1692,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1706,51 +1710,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129675462</t>
+          <t>https://artportalen.se/Sighting/129676714</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129675371</v>
+        <v>129675462</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmanstorpet, Bergmanstorpet, Mpd</t>
+          <t>Bergmanstorpet, Västeråsen  Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609172</v>
+        <v>609145</v>
       </c>
       <c r="R12" t="n">
-        <v>6919144</v>
+        <v>6919165</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,13 +1812,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129675371</t>
+          <t>https://artportalen.se/Sighting/129675462</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129675720</v>
+        <v>129675371</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1849,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609174</v>
+        <v>609172</v>
       </c>
       <c r="R13" t="n">
-        <v>6919130</v>
+        <v>6919144</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,13 +1914,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129675720</t>
+          <t>https://artportalen.se/Sighting/129675371</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129676730</v>
+        <v>129675720</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -1947,14 +1951,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+          <t>Bergmanstorpet, Bergmanstorpet, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>608827</v>
+        <v>609174</v>
       </c>
       <c r="R14" t="n">
-        <v>6919124</v>
+        <v>6919130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,6 +2015,108 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675720</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129676730</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>608827</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6919124</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129676730</t>
         </is>
@@ -2031,6 +2137,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>137214159</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137212819</v>
       </c>
       <c r="B7" t="n">
-        <v>58692</v>
+        <v>58694</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129676714</v>
       </c>
       <c r="B11" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129676714</v>
       </c>
       <c r="B11" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>137214159</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137212819</v>
       </c>
       <c r="B7" t="n">
-        <v>58694</v>
+        <v>58696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129676714</v>
       </c>
       <c r="B11" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129676714</v>
       </c>
       <c r="B11" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129676714</v>
       </c>
       <c r="B11" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129676714</v>
       </c>
       <c r="B11" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137214429</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>137214159</v>
       </c>
       <c r="B6" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137212819</v>
       </c>
       <c r="B7" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129676714</v>
       </c>
       <c r="B11" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
